--- a/Team_Roster_24.08.2026 (1).xlsx
+++ b/Team_Roster_24.08.2026 (1).xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>4:00pm-12:00pm</t>
+          <t>4:00am-12:00pm</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>9:00am-2:00am</t>
+          <t>9:00am-2:00pm</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>12:30am-5:30pm</t>
+          <t>12:30pm-5:30pm</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>20.5</v>
+        <v>15</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>5</v>
@@ -1952,19 +1952,19 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>9</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>42</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>

--- a/Team_Roster_24.08.2026 (1).xlsx
+++ b/Team_Roster_24.08.2026 (1).xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>4:00am-12:00pm</t>
+          <t>4:00pm-12:00pm</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>9:00am-2:00pm</t>
+          <t>9:00am-2:00am</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>12:30pm-5:30pm</t>
+          <t>12:30am-5:30pm</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>2:30pm-5:30pm</t>
+          <t>10:30am-5:30pm</t>
         </is>
       </c>
     </row>
@@ -962,11 +962,7 @@
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>11:30am-2:30pm</t>
-        </is>
-      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1005,7 +1001,11 @@
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2:30pm-5:30pm</t>
+        </is>
+      </c>
       <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>15</v>
+        <v>20.5</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>5</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -1829,11 +1829,11 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>$1.28</t>
+          <t>$0.00</t>
         </is>
       </c>
     </row>
@@ -1880,14 +1880,14 @@
         <v>1.5</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>$1.28</t>
+          <t>$2.56</t>
         </is>
       </c>
     </row>
@@ -1952,19 +1952,19 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>21</v>
+        <v>24.5</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>9</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>164.5</v>
+        <v>165</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
